--- a/StructureDefinition-pharmac-medication.xlsx
+++ b/StructureDefinition-pharmac-medication.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$109</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3541" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3975" uniqueCount="487">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -638,6 +638,51 @@
     <t>Indicates whether this medication is on a PHARMAC safety list.</t>
   </si>
   <si>
+    <t>Medication.extension:MedicationStrength</t>
+  </si>
+  <si>
+    <t>MedicationStrength</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir-ig.digital.health.nz/pharmac-schedules/StructureDefinition/medication-strength}
+</t>
+  </si>
+  <si>
+    <t>Medication strength</t>
+  </si>
+  <si>
+    <t>Strength for a medication.</t>
+  </si>
+  <si>
+    <t>Medication.extension:MedicationLegalClassification</t>
+  </si>
+  <si>
+    <t>MedicationLegalClassification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir-ig.digital.health.nz/pharmac-schedules/StructureDefinition/medication-legal-classification}
+</t>
+  </si>
+  <si>
+    <t>Legal classification for a medication.</t>
+  </si>
+  <si>
+    <t>Medication.extension:MedicationProductCreatedDate</t>
+  </si>
+  <si>
+    <t>MedicationProductCreatedDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir-ig.digital.health.nz/pharmac-schedules/StructureDefinition/medication-product-created-date}
+</t>
+  </si>
+  <si>
+    <t>Medication product created date</t>
+  </si>
+  <si>
+    <t>The date a medication product record was created.</t>
+  </si>
+  <si>
     <t>Medication.modifierExtension</t>
   </si>
   <si>
@@ -1082,6 +1127,45 @@
   </si>
   <si>
     <t>Medication.identifier:formulationId.assigner</t>
+  </si>
+  <si>
+    <t>Medication.identifier:gtin</t>
+  </si>
+  <si>
+    <t>gtin</t>
+  </si>
+  <si>
+    <t>GS1 GTIN</t>
+  </si>
+  <si>
+    <t>Global Trade Item Number(s) for this pack — multiple GTINs are allowed (e.g. different barcode formats)</t>
+  </si>
+  <si>
+    <t>Medication.identifier:gtin.id</t>
+  </si>
+  <si>
+    <t>Medication.identifier:gtin.extension</t>
+  </si>
+  <si>
+    <t>Medication.identifier:gtin.use</t>
+  </si>
+  <si>
+    <t>Medication.identifier:gtin.type</t>
+  </si>
+  <si>
+    <t>Medication.identifier:gtin.system</t>
+  </si>
+  <si>
+    <t>https://www.gs1.org/gtin</t>
+  </si>
+  <si>
+    <t>Medication.identifier:gtin.value</t>
+  </si>
+  <si>
+    <t>Medication.identifier:gtin.period</t>
+  </si>
+  <si>
+    <t>Medication.identifier:gtin.assigner</t>
   </si>
   <si>
     <t>Medication.code</t>
@@ -1776,12 +1860,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN97"/>
+  <dimension ref="A1:AN109"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="41.6015625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.84765625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="32.79296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="24.2890625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="25.53125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1789,7 +1873,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="91.3203125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="92.61328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -4105,43 +4189,41 @@
         <v>196</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="D21" t="s" s="2">
-        <v>197</v>
+        <v>21</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>133</v>
+        <v>198</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N21" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="O21" t="s" s="2">
-        <v>201</v>
-      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
       </c>
@@ -4189,7 +4271,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>202</v>
+        <v>138</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4198,7 +4280,7 @@
         <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>139</v>
@@ -4207,7 +4289,7 @@
         <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>21</v>
@@ -4218,43 +4300,43 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="G22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H22" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K22" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>206</v>
-      </c>
       <c r="M22" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -4291,19 +4373,19 @@
         <v>21</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>137</v>
+        <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>203</v>
+        <v>138</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4312,33 +4394,33 @@
         <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>203</v>
+        <v>132</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>21</v>
@@ -4351,26 +4433,24 @@
         <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -4419,7 +4499,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>203</v>
+        <v>138</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4428,19 +4508,19 @@
         <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>21</v>
@@ -4448,42 +4528,46 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>219</v>
+        <v>133</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
       </c>
@@ -4531,25 +4615,25 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>223</v>
+        <v>131</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>21</v>
@@ -4560,42 +4644,42 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>197</v>
+        <v>21</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>218</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>133</v>
+        <v>219</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4633,10 +4717,10 @@
         <v>21</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>136</v>
+        <v>223</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>21</v>
@@ -4645,7 +4729,7 @@
         <v>137</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4657,29 +4741,31 @@
         <v>21</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>21</v>
       </c>
@@ -4691,29 +4777,27 @@
         <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
       </c>
@@ -4737,13 +4821,13 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>236</v>
+        <v>21</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>237</v>
+        <v>21</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4761,13 +4845,13 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
@@ -4779,21 +4863,21 @@
         <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4813,23 +4897,19 @@
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
       </c>
@@ -4853,13 +4933,13 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>248</v>
+        <v>21</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>249</v>
+        <v>21</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>250</v>
+        <v>21</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -4877,7 +4957,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4889,38 +4969,38 @@
         <v>21</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>252</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>21</v>
@@ -4929,35 +5009,33 @@
         <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>259</v>
+        <v>21</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>260</v>
+        <v>21</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>21</v>
@@ -4981,51 +5059,51 @@
         <v>21</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>262</v>
+        <v>237</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>263</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5033,7 +5111,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>88</v>
@@ -5042,24 +5120,26 @@
         <v>21</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>219</v>
+        <v>108</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -5071,7 +5151,7 @@
         <v>21</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>269</v>
+        <v>21</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>21</v>
@@ -5083,13 +5163,13 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>21</v>
+        <v>251</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>21</v>
+        <v>252</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
@@ -5107,7 +5187,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5125,21 +5205,21 @@
         <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>272</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5162,16 +5242,20 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
@@ -5195,13 +5279,13 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>21</v>
+        <v>263</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>21</v>
+        <v>264</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -5219,7 +5303,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5237,21 +5321,21 @@
         <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>279</v>
+        <v>254</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>280</v>
+        <v>266</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5259,7 +5343,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>88</v>
@@ -5274,30 +5358,32 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>283</v>
+        <v>102</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>21</v>
+        <v>273</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>21</v>
+        <v>274</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>21</v>
@@ -5333,7 +5419,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5351,25 +5437,23 @@
         <v>21</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>21</v>
       </c>
@@ -5381,7 +5465,7 @@
         <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
@@ -5390,16 +5474,16 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>205</v>
+        <v>233</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>208</v>
+        <v>282</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5413,7 +5497,7 @@
         <v>21</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>21</v>
+        <v>283</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>21</v>
@@ -5449,13 +5533,13 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>203</v>
+        <v>284</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
@@ -5467,21 +5551,21 @@
         <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>211</v>
+        <v>285</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>21</v>
+        <v>286</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>218</v>
+        <v>288</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5501,16 +5585,16 @@
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>219</v>
+        <v>289</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>220</v>
+        <v>290</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>221</v>
+        <v>291</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5561,7 +5645,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>222</v>
+        <v>292</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5573,19 +5657,19 @@
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>223</v>
+        <v>293</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>21</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" hidden="true">
@@ -5593,18 +5677,18 @@
         <v>295</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>225</v>
+        <v>296</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>197</v>
+        <v>21</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>21</v>
@@ -5613,19 +5697,19 @@
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>133</v>
+        <v>297</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>226</v>
+        <v>298</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>227</v>
+        <v>299</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5663,87 +5747,87 @@
         <v>21</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>228</v>
+        <v>21</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>137</v>
+        <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>229</v>
+        <v>301</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>21</v>
+        <v>303</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="D35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>232</v>
+        <v>306</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>233</v>
+        <v>307</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
       </c>
@@ -5767,13 +5851,13 @@
         <v>21</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>236</v>
+        <v>21</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>237</v>
+        <v>21</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -5791,13 +5875,13 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>21</v>
@@ -5809,21 +5893,21 @@
         <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5843,23 +5927,19 @@
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
       </c>
@@ -5883,13 +5963,13 @@
         <v>21</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>248</v>
+        <v>21</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>249</v>
+        <v>21</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>250</v>
+        <v>21</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>21</v>
@@ -5907,7 +5987,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5919,38 +5999,38 @@
         <v>21</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>252</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>21</v>
@@ -5959,35 +6039,33 @@
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>299</v>
+        <v>21</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>260</v>
+        <v>21</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>21</v>
@@ -6011,51 +6089,51 @@
         <v>21</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>262</v>
+        <v>237</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>263</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6063,7 +6141,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>88</v>
@@ -6072,24 +6150,26 @@
         <v>21</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>219</v>
+        <v>108</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>21</v>
       </c>
@@ -6101,7 +6181,7 @@
         <v>21</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>269</v>
+        <v>21</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>21</v>
@@ -6113,13 +6193,13 @@
         <v>21</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>21</v>
+        <v>251</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>21</v>
+        <v>252</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
@@ -6137,7 +6217,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6155,21 +6235,21 @@
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>272</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6192,16 +6272,20 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>21</v>
       </c>
@@ -6225,13 +6309,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>21</v>
+        <v>263</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>21</v>
+        <v>264</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6249,7 +6333,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6267,21 +6351,21 @@
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>279</v>
+        <v>254</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>280</v>
+        <v>266</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6289,7 +6373,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>88</v>
@@ -6304,30 +6388,32 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>283</v>
+        <v>102</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>21</v>
+        <v>313</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>21</v>
+        <v>274</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>21</v>
@@ -6363,7 +6449,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6381,25 +6467,23 @@
         <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>21</v>
       </c>
@@ -6411,7 +6495,7 @@
         <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
@@ -6420,16 +6504,16 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>205</v>
+        <v>233</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>305</v>
+        <v>280</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>306</v>
+        <v>281</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>208</v>
+        <v>282</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6443,7 +6527,7 @@
         <v>21</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>21</v>
+        <v>283</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>21</v>
@@ -6479,13 +6563,13 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>203</v>
+        <v>284</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
@@ -6497,21 +6581,21 @@
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>211</v>
+        <v>285</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>21</v>
+        <v>286</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>218</v>
+        <v>288</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6531,16 +6615,16 @@
         <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>219</v>
+        <v>289</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>220</v>
+        <v>290</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>221</v>
+        <v>291</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6591,7 +6675,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>222</v>
+        <v>292</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6603,38 +6687,38 @@
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>223</v>
+        <v>293</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>21</v>
+        <v>294</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>225</v>
+        <v>296</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>197</v>
+        <v>21</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>21</v>
@@ -6643,19 +6727,19 @@
         <v>21</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>133</v>
+        <v>297</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>226</v>
+        <v>298</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>227</v>
+        <v>299</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6693,87 +6777,87 @@
         <v>21</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>228</v>
+        <v>21</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>137</v>
+        <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>229</v>
+        <v>301</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>21</v>
+        <v>303</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>232</v>
+        <v>319</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>233</v>
+        <v>320</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
       </c>
@@ -6797,13 +6881,13 @@
         <v>21</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>236</v>
+        <v>21</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>237</v>
+        <v>21</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>21</v>
@@ -6821,13 +6905,13 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
@@ -6839,21 +6923,21 @@
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6873,23 +6957,19 @@
         <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
       </c>
@@ -6913,13 +6993,13 @@
         <v>21</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>248</v>
+        <v>21</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>249</v>
+        <v>21</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>250</v>
+        <v>21</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>21</v>
@@ -6937,7 +7017,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6949,38 +7029,38 @@
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>252</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
@@ -6989,35 +7069,33 @@
         <v>21</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>312</v>
+        <v>21</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>260</v>
+        <v>21</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>21</v>
@@ -7041,51 +7119,51 @@
         <v>21</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>262</v>
+        <v>237</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>263</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7093,7 +7171,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>88</v>
@@ -7102,24 +7180,26 @@
         <v>21</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>219</v>
+        <v>108</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7131,7 +7211,7 @@
         <v>21</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>269</v>
+        <v>21</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>21</v>
@@ -7143,13 +7223,13 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>21</v>
+        <v>251</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>21</v>
+        <v>252</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7167,7 +7247,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7185,21 +7265,21 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>272</v>
+        <v>131</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7222,16 +7302,20 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
       </c>
@@ -7255,13 +7339,13 @@
         <v>21</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>21</v>
+        <v>263</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>21</v>
+        <v>264</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>21</v>
@@ -7279,7 +7363,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7297,21 +7381,21 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>279</v>
+        <v>254</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>280</v>
+        <v>266</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7319,7 +7403,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>88</v>
@@ -7334,30 +7418,32 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>283</v>
+        <v>102</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>21</v>
+        <v>326</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>21</v>
+        <v>274</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>21</v>
@@ -7393,7 +7479,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7411,37 +7497,35 @@
         <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
@@ -7450,16 +7534,16 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>205</v>
+        <v>233</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>318</v>
+        <v>280</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>319</v>
+        <v>281</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>208</v>
+        <v>282</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7473,7 +7557,7 @@
         <v>21</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>21</v>
+        <v>283</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>21</v>
@@ -7509,13 +7593,13 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>203</v>
+        <v>284</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
@@ -7527,21 +7611,21 @@
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>211</v>
+        <v>285</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>21</v>
+        <v>286</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>218</v>
+        <v>288</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7561,16 +7645,16 @@
         <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>219</v>
+        <v>289</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>220</v>
+        <v>290</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>221</v>
+        <v>291</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7621,7 +7705,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>222</v>
+        <v>292</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7633,38 +7717,38 @@
         <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>223</v>
+        <v>293</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>21</v>
+        <v>294</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>225</v>
+        <v>296</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>197</v>
+        <v>21</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -7673,19 +7757,19 @@
         <v>21</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>133</v>
+        <v>297</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>226</v>
+        <v>298</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>227</v>
+        <v>299</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7723,53 +7807,55 @@
         <v>21</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>228</v>
+        <v>21</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>137</v>
+        <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>229</v>
+        <v>301</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>21</v>
+        <v>303</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="C53" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="D53" t="s" s="2">
         <v>21</v>
       </c>
@@ -7781,29 +7867,27 @@
         <v>88</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>232</v>
+        <v>332</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>233</v>
+        <v>333</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
@@ -7827,13 +7911,13 @@
         <v>21</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>236</v>
+        <v>21</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>237</v>
+        <v>21</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -7851,13 +7935,13 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
@@ -7869,21 +7953,21 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7903,23 +7987,19 @@
         <v>21</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -7943,13 +8023,13 @@
         <v>21</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>248</v>
+        <v>21</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>249</v>
+        <v>21</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>250</v>
+        <v>21</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -7967,7 +8047,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7979,38 +8059,38 @@
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>252</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>21</v>
@@ -8019,35 +8099,33 @@
         <v>21</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>325</v>
+        <v>21</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>260</v>
+        <v>21</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>21</v>
@@ -8071,51 +8149,51 @@
         <v>21</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>262</v>
+        <v>237</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>263</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8123,7 +8201,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>88</v>
@@ -8132,24 +8210,26 @@
         <v>21</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>219</v>
+        <v>108</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
@@ -8161,7 +8241,7 @@
         <v>21</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>269</v>
+        <v>21</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>21</v>
@@ -8173,13 +8253,13 @@
         <v>21</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>21</v>
+        <v>251</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>21</v>
+        <v>252</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>21</v>
@@ -8197,7 +8277,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8215,21 +8295,21 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>272</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8252,16 +8332,20 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8285,13 +8369,13 @@
         <v>21</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>21</v>
+        <v>263</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>21</v>
+        <v>264</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>21</v>
@@ -8309,7 +8393,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8327,21 +8411,21 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>279</v>
+        <v>254</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>280</v>
+        <v>266</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8349,7 +8433,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>88</v>
@@ -8364,30 +8448,32 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>283</v>
+        <v>102</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>21</v>
+        <v>339</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T58" t="s" s="2">
-        <v>21</v>
+        <v>274</v>
       </c>
       <c r="U58" t="s" s="2">
         <v>21</v>
@@ -8423,7 +8509,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8441,37 +8527,35 @@
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>21</v>
@@ -8480,16 +8564,16 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>205</v>
+        <v>233</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>331</v>
+        <v>280</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>208</v>
+        <v>282</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8503,7 +8587,7 @@
         <v>21</v>
       </c>
       <c r="T59" t="s" s="2">
-        <v>21</v>
+        <v>283</v>
       </c>
       <c r="U59" t="s" s="2">
         <v>21</v>
@@ -8539,13 +8623,13 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>203</v>
+        <v>284</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
@@ -8557,21 +8641,21 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>211</v>
+        <v>285</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>21</v>
+        <v>286</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>218</v>
+        <v>288</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8591,16 +8675,16 @@
         <v>21</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>219</v>
+        <v>289</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>220</v>
+        <v>290</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>221</v>
+        <v>291</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8651,7 +8735,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>222</v>
+        <v>292</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8663,38 +8747,38 @@
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>223</v>
+        <v>293</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>21</v>
+        <v>294</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>225</v>
+        <v>296</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>197</v>
+        <v>21</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
@@ -8703,19 +8787,19 @@
         <v>21</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>133</v>
+        <v>297</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>226</v>
+        <v>298</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>227</v>
+        <v>299</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8753,53 +8837,55 @@
         <v>21</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>228</v>
+        <v>21</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>137</v>
+        <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>229</v>
+        <v>301</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>21</v>
+        <v>303</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="C62" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="D62" t="s" s="2">
         <v>21</v>
       </c>
@@ -8811,29 +8897,27 @@
         <v>88</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J62" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>232</v>
+        <v>345</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>233</v>
+        <v>346</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -8857,13 +8941,13 @@
         <v>21</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>236</v>
+        <v>21</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>237</v>
+        <v>21</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>21</v>
@@ -8881,13 +8965,13 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
@@ -8899,21 +8983,21 @@
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8933,23 +9017,19 @@
         <v>21</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
@@ -8973,13 +9053,13 @@
         <v>21</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>248</v>
+        <v>21</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>249</v>
+        <v>21</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>250</v>
+        <v>21</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>21</v>
@@ -8997,7 +9077,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9009,38 +9089,38 @@
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>252</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>21</v>
@@ -9049,35 +9129,33 @@
         <v>21</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>338</v>
+        <v>21</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>260</v>
+        <v>21</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>21</v>
@@ -9101,51 +9179,51 @@
         <v>21</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>262</v>
+        <v>237</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>263</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9153,7 +9231,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>88</v>
@@ -9162,24 +9240,26 @@
         <v>21</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>219</v>
+        <v>108</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
@@ -9191,7 +9271,7 @@
         <v>21</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>269</v>
+        <v>21</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>21</v>
@@ -9203,13 +9283,13 @@
         <v>21</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>21</v>
+        <v>251</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>21</v>
+        <v>252</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>21</v>
@@ -9227,7 +9307,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9245,21 +9325,21 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>272</v>
+        <v>131</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9282,16 +9362,20 @@
         <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9315,13 +9399,13 @@
         <v>21</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>21</v>
+        <v>263</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>21</v>
+        <v>264</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
@@ -9339,7 +9423,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9357,21 +9441,21 @@
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>279</v>
+        <v>254</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>280</v>
+        <v>266</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9379,7 +9463,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>88</v>
@@ -9394,30 +9478,32 @@
         <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>283</v>
+        <v>102</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>21</v>
+        <v>352</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>21</v>
+        <v>274</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>21</v>
@@ -9453,7 +9539,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9471,21 +9557,21 @@
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>342</v>
+        <v>279</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9499,7 +9585,7 @@
         <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>21</v>
@@ -9508,16 +9594,16 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>343</v>
+        <v>280</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>344</v>
+        <v>281</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>345</v>
+        <v>282</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9531,7 +9617,7 @@
         <v>21</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>21</v>
+        <v>283</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>21</v>
@@ -9543,13 +9629,13 @@
         <v>21</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>248</v>
+        <v>21</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>346</v>
+        <v>21</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>347</v>
+        <v>21</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>21</v>
@@ -9567,7 +9653,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>342</v>
+        <v>284</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9582,24 +9668,24 @@
         <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>348</v>
+        <v>21</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>349</v>
+        <v>285</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>350</v>
+        <v>21</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>351</v>
+        <v>286</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>352</v>
+        <v>288</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9619,16 +9705,16 @@
         <v>21</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>219</v>
+        <v>289</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>220</v>
+        <v>290</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>221</v>
+        <v>291</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9679,7 +9765,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>222</v>
+        <v>292</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9691,38 +9777,38 @@
         <v>21</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>223</v>
+        <v>293</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>21</v>
+        <v>294</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>353</v>
+        <v>296</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>197</v>
+        <v>21</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>21</v>
@@ -9731,19 +9817,19 @@
         <v>21</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>133</v>
+        <v>297</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>226</v>
+        <v>298</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>227</v>
+        <v>299</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9781,53 +9867,55 @@
         <v>21</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>228</v>
+        <v>21</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>137</v>
+        <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>229</v>
+        <v>301</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>21</v>
+        <v>303</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C71" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="D71" t="s" s="2">
         <v>21</v>
       </c>
@@ -9839,7 +9927,7 @@
         <v>80</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>21</v>
@@ -9848,20 +9936,18 @@
         <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>355</v>
+        <v>219</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>21</v>
       </c>
@@ -9909,7 +9995,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>360</v>
+        <v>217</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -9927,21 +10013,21 @@
         <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>361</v>
+        <v>225</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>362</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>363</v>
+        <v>232</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9949,35 +10035,31 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>143</v>
+        <v>234</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>21</v>
       </c>
@@ -10025,7 +10107,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>367</v>
+        <v>236</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10037,59 +10119,59 @@
         <v>21</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>368</v>
+        <v>237</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>369</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>370</v>
+        <v>239</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>371</v>
+        <v>240</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>372</v>
+        <v>241</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>373</v>
+        <v>214</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10097,7 +10179,7 @@
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" t="s" s="2">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="S73" t="s" s="2">
         <v>21</v>
@@ -10115,49 +10197,49 @@
         <v>21</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>236</v>
+        <v>21</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>374</v>
+        <v>21</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>375</v>
+        <v>21</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>370</v>
+        <v>243</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>376</v>
+        <v>237</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>21</v>
@@ -10168,10 +10250,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>377</v>
+        <v>245</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10188,22 +10270,26 @@
         <v>21</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>283</v>
+        <v>108</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>378</v>
+        <v>246</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
       </c>
@@ -10227,13 +10313,13 @@
         <v>21</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>21</v>
+        <v>251</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>21</v>
+        <v>252</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>21</v>
@@ -10251,7 +10337,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>377</v>
+        <v>253</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10266,24 +10352,24 @@
         <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>380</v>
+        <v>21</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>381</v>
+        <v>254</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>382</v>
+        <v>21</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>383</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>384</v>
+        <v>363</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>384</v>
+        <v>256</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10291,33 +10377,35 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K75" t="s" s="2">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>385</v>
+        <v>258</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>386</v>
+        <v>259</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O75" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>21</v>
       </c>
@@ -10341,13 +10429,13 @@
         <v>21</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>388</v>
+        <v>262</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>389</v>
+        <v>263</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>390</v>
+        <v>264</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>21</v>
@@ -10365,7 +10453,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>384</v>
+        <v>265</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10380,24 +10468,24 @@
         <v>100</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>391</v>
+        <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>392</v>
+        <v>254</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>393</v>
+        <v>266</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>394</v>
+        <v>364</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>394</v>
+        <v>268</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10405,7 +10493,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>88</v>
@@ -10417,31 +10505,35 @@
         <v>21</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>219</v>
+        <v>102</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>220</v>
+        <v>269</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+        <v>270</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>21</v>
+        <v>365</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T76" t="s" s="2">
-        <v>21</v>
+        <v>274</v>
       </c>
       <c r="U76" t="s" s="2">
         <v>21</v>
@@ -10477,7 +10569,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>222</v>
+        <v>275</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10489,38 +10581,38 @@
         <v>21</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>223</v>
+        <v>276</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>21</v>
+        <v>277</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>395</v>
+        <v>366</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>395</v>
+        <v>279</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>197</v>
+        <v>21</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>21</v>
@@ -10529,19 +10621,19 @@
         <v>21</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>133</v>
+        <v>233</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>226</v>
+        <v>280</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>227</v>
+        <v>281</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>200</v>
+        <v>282</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10555,7 +10647,7 @@
         <v>21</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>21</v>
+        <v>283</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>21</v>
@@ -10579,51 +10671,51 @@
         <v>21</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>228</v>
+        <v>21</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>137</v>
+        <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>229</v>
+        <v>284</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>223</v>
+        <v>285</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>21</v>
+        <v>286</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>396</v>
+        <v>367</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>396</v>
+        <v>288</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10634,7 +10726,7 @@
         <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>21</v>
@@ -10646,20 +10738,16 @@
         <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>355</v>
+        <v>289</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>356</v>
+        <v>290</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>21</v>
       </c>
@@ -10707,13 +10795,13 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>360</v>
+        <v>292</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>21</v>
@@ -10725,21 +10813,21 @@
         <v>21</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>361</v>
+        <v>293</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>362</v>
+        <v>294</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>397</v>
+        <v>368</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>397</v>
+        <v>296</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10762,20 +10850,18 @@
         <v>89</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>219</v>
+        <v>297</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>398</v>
+        <v>298</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>399</v>
+        <v>299</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>21</v>
       </c>
@@ -10823,7 +10909,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>367</v>
+        <v>301</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -10841,21 +10927,21 @@
         <v>21</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>368</v>
+        <v>302</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN79" t="s" s="2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
         <v>369</v>
       </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>400</v>
-      </c>
       <c r="B80" t="s" s="2">
-        <v>400</v>
+        <v>369</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10863,13 +10949,13 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>21</v>
@@ -10878,15 +10964,17 @@
         <v>89</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>401</v>
+        <v>257</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>402</v>
+        <v>370</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>371</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>372</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>21</v>
@@ -10911,13 +10999,13 @@
         <v>21</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>21</v>
+        <v>373</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>21</v>
+        <v>374</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>21</v>
@@ -10935,7 +11023,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>400</v>
+        <v>369</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -10950,24 +11038,24 @@
         <v>100</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>21</v>
+        <v>375</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>404</v>
+        <v>376</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>21</v>
+        <v>377</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>21</v>
+        <v>378</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>405</v>
+        <v>379</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>405</v>
+        <v>379</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10978,10 +11066,10 @@
         <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>21</v>
@@ -10990,17 +11078,15 @@
         <v>21</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>406</v>
+        <v>233</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>407</v>
+        <v>234</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>409</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>21</v>
@@ -11049,25 +11135,25 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>405</v>
+        <v>236</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>410</v>
+        <v>237</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>21</v>
@@ -11078,21 +11164,21 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>411</v>
+        <v>380</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>411</v>
+        <v>380</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>21</v>
@@ -11104,15 +11190,17 @@
         <v>21</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>219</v>
+        <v>133</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>21</v>
@@ -11149,37 +11237,37 @@
         <v>21</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>21</v>
@@ -11190,14 +11278,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>412</v>
+        <v>381</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>412</v>
+        <v>381</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>197</v>
+        <v>21</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -11213,21 +11301,23 @@
         <v>21</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>133</v>
+        <v>382</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>226</v>
+        <v>383</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>227</v>
+        <v>384</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="O83" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>21</v>
       </c>
@@ -11275,7 +11365,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>229</v>
+        <v>387</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11287,62 +11377,62 @@
         <v>21</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>223</v>
+        <v>388</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>21</v>
+        <v>389</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
-        <v>413</v>
+        <v>390</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>413</v>
+        <v>390</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>414</v>
+        <v>21</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J84" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>133</v>
+        <v>233</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>415</v>
+        <v>143</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>416</v>
+        <v>391</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>200</v>
+        <v>392</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>201</v>
+        <v>393</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
@@ -11391,39 +11481,39 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>417</v>
+        <v>394</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>131</v>
+        <v>395</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>21</v>
+        <v>396</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
-        <v>418</v>
+        <v>397</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>418</v>
+        <v>397</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11437,33 +11527,33 @@
         <v>88</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>243</v>
+        <v>108</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>419</v>
+        <v>398</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>21</v>
@@ -11481,13 +11571,13 @@
         <v>21</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>422</v>
+        <v>401</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>347</v>
+        <v>402</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>21</v>
@@ -11505,10 +11595,10 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>418</v>
+        <v>397</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>88</v>
@@ -11520,24 +11610,24 @@
         <v>100</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>348</v>
+        <v>21</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>424</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>425</v>
+        <v>404</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>425</v>
+        <v>404</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11557,16 +11647,16 @@
         <v>21</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>219</v>
+        <v>297</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>220</v>
+        <v>405</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>221</v>
+        <v>406</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11617,7 +11707,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>222</v>
+        <v>404</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -11629,41 +11719,41 @@
         <v>21</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>21</v>
+        <v>407</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>223</v>
+        <v>408</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>21</v>
+        <v>409</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>21</v>
+        <v>410</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>197</v>
+        <v>21</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>21</v>
@@ -11672,16 +11762,16 @@
         <v>21</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>133</v>
+        <v>257</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>226</v>
+        <v>412</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>227</v>
+        <v>413</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>200</v>
+        <v>414</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11707,63 +11797,63 @@
         <v>21</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>21</v>
+        <v>415</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>21</v>
+        <v>416</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>21</v>
+        <v>417</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>228</v>
+        <v>21</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>137</v>
+        <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>229</v>
+        <v>411</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>21</v>
+        <v>418</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>223</v>
+        <v>419</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>21</v>
+        <v>420</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11774,7 +11864,7 @@
         <v>79</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>21</v>
@@ -11783,23 +11873,19 @@
         <v>21</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>355</v>
+        <v>233</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>356</v>
+        <v>234</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>21</v>
       </c>
@@ -11847,50 +11933,50 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>360</v>
+        <v>236</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>361</v>
+        <v>237</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>362</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>21</v>
@@ -11899,23 +11985,21 @@
         <v>21</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>219</v>
+        <v>133</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>429</v>
+        <v>240</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>430</v>
+        <v>241</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>21</v>
       </c>
@@ -11951,51 +12035,51 @@
         <v>21</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>367</v>
+        <v>243</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>368</v>
+        <v>237</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>369</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12003,34 +12087,34 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J90" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K90" t="s" s="2">
-        <v>432</v>
+        <v>382</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>433</v>
+        <v>383</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>434</v>
+        <v>384</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>435</v>
+        <v>385</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>436</v>
+        <v>386</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>21</v>
@@ -12079,13 +12163,13 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>431</v>
+        <v>387</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>21</v>
@@ -12097,21 +12181,21 @@
         <v>21</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>437</v>
+        <v>388</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>21</v>
+        <v>389</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12131,19 +12215,23 @@
         <v>21</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>401</v>
+        <v>233</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>439</v>
+        <v>425</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>21</v>
       </c>
@@ -12191,7 +12279,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>438</v>
+        <v>394</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12206,24 +12294,24 @@
         <v>100</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>441</v>
+        <v>21</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>442</v>
+        <v>396</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12243,16 +12331,16 @@
         <v>21</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12303,7 +12391,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12318,10 +12406,10 @@
         <v>100</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>380</v>
+        <v>21</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>21</v>
@@ -12330,12 +12418,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12346,10 +12434,10 @@
         <v>79</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>21</v>
@@ -12358,15 +12446,17 @@
         <v>21</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>219</v>
+        <v>433</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>220</v>
+        <v>434</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N93" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>21</v>
@@ -12415,25 +12505,25 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>222</v>
+        <v>432</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>223</v>
+        <v>437</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>21</v>
@@ -12444,21 +12534,21 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>197</v>
+        <v>21</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>21</v>
@@ -12470,17 +12560,15 @@
         <v>21</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>133</v>
+        <v>233</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>21</v>
@@ -12529,25 +12617,25 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>21</v>
@@ -12558,14 +12646,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>414</v>
+        <v>211</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -12578,26 +12666,24 @@
         <v>21</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>415</v>
+        <v>240</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>416</v>
+        <v>241</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>21</v>
       </c>
@@ -12645,7 +12731,7 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>417</v>
+        <v>243</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -12663,7 +12749,7 @@
         <v>21</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>131</v>
+        <v>237</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>21</v>
@@ -12674,42 +12760,46 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>21</v>
+        <v>441</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>219</v>
+        <v>133</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>21</v>
       </c>
@@ -12757,39 +12847,39 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>380</v>
+        <v>21</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>211</v>
+        <v>131</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>453</v>
+        <v>21</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12797,7 +12887,7 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>88</v>
@@ -12812,16 +12902,18 @@
         <v>21</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>455</v>
+        <v>257</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
+      <c r="O97" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>21</v>
       </c>
@@ -12845,13 +12937,13 @@
         <v>21</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>21</v>
+        <v>449</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>21</v>
+        <v>374</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>21</v>
@@ -12869,10 +12961,10 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>88</v>
@@ -12884,20 +12976,1384 @@
         <v>100</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="AL97" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="AM97" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN97" t="s" s="2">
+      <c r="B102" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K102" t="s" s="2">
         <v>459</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="P102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="P107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
+      <c r="P108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2"/>
+      <c r="P109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>486</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN97">
+  <autoFilter ref="A1:AN109">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12907,7 +14363,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI96">
+  <conditionalFormatting sqref="A2:AI108">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-pharmac-medication.xlsx
+++ b/StructureDefinition-pharmac-medication.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
